--- a/DevOps/ExcelToJsonConverter/products-data.xlsx
+++ b/DevOps/ExcelToJsonConverter/products-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Schema" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="118">
   <si>
     <t>fieldName</t>
   </si>
@@ -284,6 +284,97 @@
   </si>
   <si>
     <t>1-3</t>
+  </si>
+  <si>
+    <t>MM-WP-203AN</t>
+  </si>
+  <si>
+    <t>2-in-1 Wooden Alphabet and Numbers 1-20 Puzzle Combo | ABC &amp; 123 Learning Set with Easy-Grip Knobs | 9mm Extra Thick Boards | Montessori STEM &amp; Literacy Toys for Preschoolers</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0H15BM7XY</t>
+  </si>
+  <si>
+    <t>/shop/8</t>
+  </si>
+  <si>
+    <t>&lt;ul style='list-style-type: square;'&gt;&lt;li&gt;2 Wooden Boards of Alphabets and Number&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>MM-WP-201AHS</t>
+  </si>
+  <si>
+    <t>2-in-1 Wooden Hindi Swar and English Alphabet Puzzle Combo | Varnamala &amp; ABC Learning Set with Easy-Grip Knobs | 9mm Extra Thick Boards | Bilingual Literacy Toys for Kids</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0H157PPHS</t>
+  </si>
+  <si>
+    <t>/shop/9</t>
+  </si>
+  <si>
+    <t>Wooden Fruit and Vegetable Puzzle Set for Toddlers | 2-in-1 Combo Pack with Easy-Grip Knobs | 9mm Extra Thick Durable Boards | Montessori Learning Toys for Healthy Habits</t>
+  </si>
+  <si>
+    <t>MM-WP-202FV</t>
+  </si>
+  <si>
+    <t>/img/wooden/puzzle/Combo_Fruit_Veg/MAIN.jpg|/img/wooden/puzzle/Combo_Fruit_Veg/PT03.jpg|/img/wooden/puzzle/Combo_Fruit_Veg/PT02.jpg|/img/wooden/puzzle/Combo_Fruit_Veg/PT01.jpg|/img/wooden/puzzle/Combo_Fruit_Veg/PT04.jpg|/img/wooden/puzzle/Combo_Fruit_Veg/PT05.jpg</t>
+  </si>
+  <si>
+    <t>/img/wooden/puzzle/Combo_Alphabet_Hindi_swar/MAIN.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar/PT02.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar/PT03.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar/PT01.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar/PT04.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar/PT05.jpg</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0H156CBC3</t>
+  </si>
+  <si>
+    <t>/shop/10</t>
+  </si>
+  <si>
+    <t>&lt;ul style='list-style-type: square;'&gt;&lt;li&gt;2 Wooden Boards of Fruit and Vegetable&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ul style='list-style-type: square;'&gt;&lt;li&gt;2 Wooden Boards of Alphabets and Hindi Swarr&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>3-in-1 Wooden Alphabet, Numbers &amp; Shapes Puzzle Set | Early Learning Combo with Easy-Grip Knobs | 9mm Extra Thick Durable Boards | Montessori STEM Toy for Toddlers</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0H153PLZ1</t>
+  </si>
+  <si>
+    <t>/shop/11</t>
+  </si>
+  <si>
+    <t>&lt;ul style='list-style-type: square;'&gt;&lt;li&gt;3 Wooden Boards of Alphabets, Numbers and Shapes&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>/img/wooden/puzzle/Combo_Alphabet_Number_Shapes/MAIN.jpg|/img/wooden/puzzle/Combo_Alphabet_Number_Shapes/PT01.jpg|/img/wooden/puzzle/Combo_Alphabet_Number_Shapes/PT05.jpg|/img/wooden/puzzle/Combo_Alphabet_Number_Shapes/PT02.jpg|/img/wooden/puzzle/Combo_Alphabet_Number_Shapes/PT03.jpg|/img/wooden/puzzle/Combo_Alphabet_Number_Shapes/PT04.jpg</t>
+  </si>
+  <si>
+    <t>MM-WP-302ANS</t>
+  </si>
+  <si>
+    <t>MM-WP-301ANHS</t>
+  </si>
+  <si>
+    <t>3-in-1 Wooden Hindi Swar, Alphabet &amp; Numbers Puzzle Set | Varnamala, ABC &amp; 123 Combo with Easy-Grip Knobs | 9mm Extra Thick Boards | Montessori Language &amp; Math Toys</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0H159RMKM</t>
+  </si>
+  <si>
+    <t>/shop/12</t>
+  </si>
+  <si>
+    <t>&lt;ul style='list-style-type: square;'&gt;&lt;li&gt;3 Wooden Boards of Alphabets, Numbers and Hindi Swar&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/img/wooden/puzzle/Combo_Alphabet_Hindi_swar_Number/MAIN.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar_Number/PT01.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar_Number/PT05.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar_Number/PT02.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar_Number/PT03.jpg|/img/wooden/puzzle/Combo_Alphabet_Hindi_swar_Number/PT04.jpg
+</t>
+  </si>
+  <si>
+    <t>/img/wooden/puzzle/Combo_Alphabet_Number/MAIN.png|/img/wooden/puzzle/Combo_Alphabet_Number/PT01.jpg|/img/wooden/puzzle/Combo_Alphabet_Number/PT03.jpg|/img/wooden/puzzle/Combo_Alphabet_Number/PT02.jpg|/img/wooden/puzzle/Combo_Alphabet_Number/PT04.jpg|/img/wooden/puzzle/Combo_Alphabet_Number/PT05.jpg</t>
   </si>
 </sst>
 </file>
@@ -293,7 +384,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -328,6 +419,20 @@
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -367,7 +472,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -422,6 +527,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -549,13 +660,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="13"/>
+    <col min="1" max="1" width="16.140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -563,7 +674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
@@ -571,7 +682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>8</v>
       </c>
@@ -579,7 +690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>19</v>
       </c>
@@ -587,7 +698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>4</v>
       </c>
@@ -595,7 +706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>5</v>
       </c>
@@ -603,7 +714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>15</v>
       </c>
@@ -611,7 +722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>24</v>
       </c>
@@ -619,7 +730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>13</v>
       </c>
@@ -627,7 +738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>6</v>
       </c>
@@ -635,7 +746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>16</v>
       </c>
@@ -643,7 +754,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>17</v>
       </c>
@@ -651,7 +762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>18</v>
       </c>
@@ -659,7 +770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>25</v>
       </c>
@@ -667,7 +778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>10</v>
       </c>
@@ -675,7 +786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>12</v>
       </c>
@@ -683,7 +794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>26</v>
       </c>
@@ -691,7 +802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>27</v>
       </c>
@@ -699,7 +810,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>28</v>
       </c>
@@ -707,7 +818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>29</v>
       </c>
@@ -715,7 +826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
         <v>30</v>
       </c>
@@ -736,22 +847,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T31"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" customWidth="1"/>
-    <col min="6" max="6" width="33.21875" customWidth="1"/>
-    <col min="7" max="7" width="20.88671875" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="18"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="47.7109375" customWidth="1"/>
+    <col min="7" max="7" width="44.140625" customWidth="1"/>
+    <col min="8" max="8" width="36.42578125" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="18"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.44140625" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>2</v>
       </c>
@@ -813,7 +926,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="196.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="196.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -872,7 +985,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="193.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -931,7 +1044,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="139.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="139.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -990,7 +1103,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="182.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="182.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1049,7 +1162,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1108,7 +1221,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="159" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="159" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1167,7 +1280,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="189" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="189" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1226,73 +1339,353 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L9"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L10"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L11"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L12"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L13"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="382.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I9" s="3">
+        <v>289</v>
+      </c>
+      <c r="J9" s="3">
+        <v>549</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="S9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="382.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>299</v>
+      </c>
+      <c r="J10" s="3">
+        <v>549</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="S10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="382.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="3">
+        <v>289</v>
+      </c>
+      <c r="J11" s="3">
+        <v>549</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="S11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="382.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I12" s="3">
+        <v>429</v>
+      </c>
+      <c r="J12" s="3">
+        <v>689</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="S12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="382.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" s="3">
+        <v>469</v>
+      </c>
+      <c r="J13" s="3">
+        <v>689</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="S13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="L14"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="L15"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="L16"/>
     </row>
-    <row r="17" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L17"/>
     </row>
-    <row r="18" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L18"/>
     </row>
-    <row r="19" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L19"/>
     </row>
-    <row r="20" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L20"/>
     </row>
-    <row r="21" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L21"/>
     </row>
-    <row r="22" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L22"/>
     </row>
-    <row r="23" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L23"/>
     </row>
-    <row r="24" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L24"/>
     </row>
-    <row r="25" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L25"/>
     </row>
-    <row r="26" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L26"/>
     </row>
-    <row r="27" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L27"/>
     </row>
-    <row r="28" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L28"/>
     </row>
-    <row r="29" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L29"/>
     </row>
-    <row r="30" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L30"/>
     </row>
-    <row r="31" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L31"/>
     </row>
   </sheetData>
@@ -1304,9 +1697,14 @@
     <hyperlink ref="L2" r:id="rId5"/>
     <hyperlink ref="L6" r:id="rId6"/>
     <hyperlink ref="L8" r:id="rId7"/>
+    <hyperlink ref="L9" r:id="rId8"/>
+    <hyperlink ref="L10" r:id="rId9"/>
+    <hyperlink ref="L11" r:id="rId10"/>
+    <hyperlink ref="L12" r:id="rId11"/>
+    <hyperlink ref="L13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId13"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/DevOps/ExcelToJsonConverter/products-data.xlsx
+++ b/DevOps/ExcelToJsonConverter/products-data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Schema" sheetId="1" r:id="rId1"/>

--- a/DevOps/ExcelToJsonConverter/products-data.xlsx
+++ b/DevOps/ExcelToJsonConverter/products-data.xlsx
@@ -815,7 +815,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">

--- a/DevOps/ExcelToJsonConverter/products-data.xlsx
+++ b/DevOps/ExcelToJsonConverter/products-data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Schema" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="130">
   <si>
     <t>fieldName</t>
   </si>
@@ -375,6 +375,42 @@
   </si>
   <si>
     <t>/img/wooden/puzzle/Combo_Alphabet_Number/MAIN.png|/img/wooden/puzzle/Combo_Alphabet_Number/PT01.jpg|/img/wooden/puzzle/Combo_Alphabet_Number/PT03.jpg|/img/wooden/puzzle/Combo_Alphabet_Number/PT02.jpg|/img/wooden/puzzle/Combo_Alphabet_Number/PT04.jpg|/img/wooden/puzzle/Combo_Alphabet_Number/PT05.jpg</t>
+  </si>
+  <si>
+    <t>MM-ET-101MK</t>
+  </si>
+  <si>
+    <t>Voice Control Banana Dancing Monkey Toy | Spinning, Rolling and Tumbling Toy for Kids with Bright LED Lights &amp; Sound Effects</t>
+  </si>
+  <si>
+    <t>/img/toys/monkey_toy/dimensions.png|/img/toys/monkey_toy/features.png|/img/toys/monkey_toy/Front Image1.png</t>
+  </si>
+  <si>
+    <t>/shop/13</t>
+  </si>
+  <si>
+    <t>toys</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>&lt;ul style='list-style-type: square;'&gt;&lt;li&gt;1 Monkey Toy&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>MM-CR-101RT</t>
+  </si>
+  <si>
+    <t>/img/stationary/chocolate_rubber/main_image.png|/img/stationary/chocolate_rubber/2image.png|/img/stationary/chocolate_rubber/3_image.png|/img/stationary/chocolate_rubber/4_image.png|/img/stationary/chocolate_rubber/5image.png</t>
+  </si>
+  <si>
+    <t>/shop/14</t>
+  </si>
+  <si>
+    <t>&lt;ul style='list-style-type: square;'&gt;&lt;li&gt;2 choclate Rubber&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>Chocalate Rubber</t>
   </si>
 </sst>
 </file>
@@ -1634,14 +1670,164 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="L14"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="L15"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="L16"/>
+    <row r="14" spans="1:20" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="3">
+        <v>175</v>
+      </c>
+      <c r="J14" s="3">
+        <v>699</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="17"/>
+      <c r="M14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="S14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="3">
+        <v>175</v>
+      </c>
+      <c r="J15" s="3">
+        <v>699</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" s="17"/>
+      <c r="M15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="S15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" s="3">
+        <v>70</v>
+      </c>
+      <c r="J16" s="3">
+        <v>150</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" s="17"/>
+      <c r="M16" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R16" s="9">
+        <v>46145</v>
+      </c>
+      <c r="S16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="17" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L17"/>
